--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0103.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0103.xlsx
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Ném cho ta một viên gel năng lượng đi.</t>
+          <t>Ném cho tao một viên gel năng lượng đi.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>...Ừ. Khoa học Vật liệu. Lớp phủ pha. Cậu tự hại mình rồi đấy. Khi một đơn vị TARD-E hát đòi cậu đầu hàng, ta mà không quay lại mới lạ.</t>
+          <t>...Ừ. Khoa học Vật liệu. Lớp phủ pha. Cậu tự hại mình rồi đấy. Khi một đơn vị TARD-E hát đòi cậu đầu hàng, tao mà không quay lại mới lạ.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>À, được rồi! Thực ra, cậu có muốn tham gia Câu lạc bộ Cosplay Exoswarm của tụi mình không? Xem thử đi!</t>
+          <t>À, được rồi! Thực ra, bạn có muốn tham gia Câu lạc bộ Cosplay Exoswarm của tụi mình không? Xem thử đi!</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Nếu cậu không gọi ta dậy, ta đã phải ăn thứ đó trong mơ rồi. Thật sự, cảm ơn cậu nhiều!</t>
+          <t>Nếu cậu không gọi tao dậy, tao đã phải ăn thứ đó trong mơ rồi. Thật sự, cảm ơn cậu nhiều!</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Ui, nhìn góc này mặt ta sưng húp thế này... Biết thế đừng thức khuya nữa.</t>
+          <t>Ui, nhìn góc này mặt tao sưng húp thế này... Biết thế đừng thức khuya nữa.</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Trong tấm này mặt ta trông thon hơn, nhưng tóc lại bù xù...</t>
+          <t>Trong tấm này mặt tao trông thon hơn, nhưng tóc lại bù xù...</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Ừ, mà... tụi ta cũng chẳng đặt tiêu chuẩn cao gì đâu. Ta chỉ mong lần sau tăng tải trọng lên, ta không bị vỡ trận thôi.</t>
+          <t>Ừ, mà... tụi tao cũng chẳng đặt tiêu chuẩn cao gì đâu. Tao chỉ mong lần sau tăng tải trọng lên, tao không bị vỡ trận thôi.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Thôi đừng nói nữa... Lần tới họ tổ chức bình chọn "Giáo sư Được Yêu Thích Nhất", ta sẽ bầu cho ông ấy!</t>
+          <t>Thôi đừng nói nữa... Lần tới họ tổ chức bình chọn "Giáo sư Được Yêu Thích Nhất", tao sẽ bầu cho ông ấy!</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Lần này chúng ta thực sự có đủ Glacier Probe rồi à? Để ta kiểm tra sổ ghi chép đã.</t>
+          <t>Lần này chúng ta thực sự có đủ Glacier Probe rồi à? Để tao kiểm tra sổ ghi chép đã.</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Đi đường vòng cho thoáng đã. Ta không muốn cắt qua Quảng Trường Tròn đâu.</t>
+          <t>Đi đường vòng cho thoáng đã. Tao không muốn cắt qua Quảng Trường Tròn đâu.</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Đi đường vòng cho thoáng đã. Ta không muốn cắt qua Quảng Trường Tròn đâu.</t>
+          <t>Đi đường vòng cho thoáng đã. Tao không muốn cắt qua Quảng Trường Tròn đâu.</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Nhưng lần trước khi ta cắt ngang qua Quảng Trường Tròn, cố vấn đã đi tìm ta... Rồi điểm số của ta tụt dốc không phanh.</t>
+          <t>Nhưng lần trước khi tao cắt ngang qua Quảng Trường Tròn, cố vấn đã đi tìm tao... Rồi điểm số của tao tụt dốc không phanh.</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Nếu sự kiện không kết thúc sớm, ta đã loại hết mọi đối thủ rồi.</t>
+          <t>Nếu sự kiện không kết thúc sớm, tao đã loại hết mọi đối thủ rồi.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Hội Học sinh vừa phản hồi đơn xin gia nhập của ta rồi.</t>
+          <t>Hội Học sinh vừa phản hồi đơn xin gia nhập của tao rồi.</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Hội Học sinh vừa phản hồi đơn xin gia nhập của ta rồi.</t>
+          <t>Hội Học sinh vừa phản hồi đơn xin gia nhập của tao rồi.</t>
         </is>
       </c>
     </row>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Thật sao? Chắc chỉ là ảo giác thôi. Ta chẳng thấy gì cả.</t>
+          <t>Thật sao? Chắc chỉ là ảo giác thôi. Tao chẳng thấy gì cả.</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Tiền bối à, bầy Exoswarm vẫn chưa có thay đổi gì cả...</t>
+          <t>bạn à, bầy Exoswarm vẫn chưa có thay đổi gì cả...</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Tiền bối à, bầy Exoswarm vẫn chưa có thay đổi gì cả...</t>
+          <t>bạn à, bầy Exoswarm vẫn chưa có thay đổi gì cả...</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Không thể tin nổi. Cậu vẫn liều lĩnh như thế à. Ta sẽ gọi ngay cố vấn của cậu để yêu cầu cắt giảm phần Tacetite của cậu đấy.</t>
+          <t>Không thể tin nổi. Cậu vẫn liều lĩnh như thế à. Tao sẽ gọi ngay cố vấn của cậu để yêu cầu cắt giảm phần Tacetite của cậu đấy.</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Sao, ta có giống loại người ngồi than vãn rồi bắt mọi người phải lo lắng không? Cứ tiếp đi. Ta muốn giúp nếu có thể.</t>
+          <t>Sao, tao có giống loại người ngồi than vãn rồi bắt mọi người phải lo lắng không? Cứ tiếp đi. Tao muốn giúp nếu có thể.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Ta đã thu thập được vài manh mối rồi. Chuẩn bị sẵn một chút. Nhưng cho ta thêm chút thời gian để sắp xếp mọi thứ đã.</t>
+          <t>Tao đã thu thập được vài manh mối rồi. Chuẩn bị sẵn một chút. Nhưng cho tao thêm chút thời gian để sắp xếp mọi thứ đã.</t>
         </is>
       </c>
     </row>
@@ -22674,7 +22674,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu có thể thay tớ đến Rừng Bjartr được không? Không hiểu sao, bọn Soliskin có vẻ sợ tớ...</t>
+          <t>{PlayerName}, cậu có thể thay tớ đến Bjartr Woods được không? Không hiểu sao, bọn Soliskin có vẻ sợ tớ...</t>
         </is>
       </c>
     </row>
@@ -22739,7 +22739,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Ta sẽ thử một phen.</t>
+          <t>Tao sẽ thử một phen.</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27484,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>{PlayerName}, cậu đây rồi. Ta đã hỏi thăm xung quanh, hóa ra lần đầu người ta nhìn thấy Ghost Miko không phải ở trong khuôn viên trường.</t>
+          <t>{PlayerName}, cậu đây rồi. Tao đã hỏi thăm xung quanh, hóa ra lần đầu người ta nhìn thấy Ghost Miko không phải ở trong khuôn viên trường.</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Và... qua những gì ta biết về cô ấy mấy ngày qua, ta không nghĩ cô ấy thích thứ gì quá mạnh hay ngọt gắt đâu.</t>
+          <t>Và... qua những gì tao biết về cô ấy mấy ngày qua, tao không nghĩ cô ấy thích thứ gì quá mạnh hay ngọt gắt đâu.</t>
         </is>
       </c>
     </row>
@@ -31384,7 +31384,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Giả định thì ta không thích lắm, {PlayerName}. Nhưng nếu đó là phỏng đoán của cậu... Phải nói là, cũng có khả năng đấy.</t>
+          <t>Giả định thì tao không thích lắm, {PlayerName}. Nhưng nếu đó là phỏng đoán của cậu... Phải nói là, cũng có khả năng đấy.</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Sau bao ngày điều tra, tuy chưa tận mắt nhìn thấy cô ấy, nhưng hình bóng mờ ảo trong ký ức của ta đang dần trở nên rõ ràng hơn.</t>
+          <t>Sau bao ngày điều tra, tuy chưa tận mắt nhìn thấy cô ấy, nhưng hình bóng mờ ảo trong ký ức của tao đang dần trở nên rõ ràng hơn.</t>
         </is>
       </c>
     </row>
